--- a/files/港岛-鲗鱼涌-君豪峰.xlsx
+++ b/files/港岛-鲗鱼涌-君豪峰.xlsx
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>6260500</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>28587</v>
+        <v>28718</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>6260500</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>28587</v>
+        <v>28718</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>9158400</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>30630</v>
+        <v>30528</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>9158400</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>30630</v>
+        <v>30528</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>6234190</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>28467</v>
+        <v>28597</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>6234190</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>28467</v>
+        <v>28597</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>6111360</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>27906</v>
+        <v>28034</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>6111360</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>27906</v>
+        <v>28034</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>8684160</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>29044</v>
+        <v>28947</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>8684160</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>29044</v>
+        <v>28947</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>6008750</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>27437</v>
+        <v>27563</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>6008750</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>27437</v>
+        <v>27563</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>5686700</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>25967</v>
+        <v>26086</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>5686700</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>25967</v>
+        <v>26086</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>5931800</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>27086</v>
+        <v>27210</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>5931800</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>27086</v>
+        <v>27210</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>5671680</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>25898</v>
+        <v>26017</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>5671680</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>25898</v>
+        <v>26017</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>5855800</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>26739</v>
+        <v>26861</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>5855800</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>26739</v>
+        <v>26861</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>8360430</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>27961</v>
+        <v>27868</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>8360430</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>27961</v>
+        <v>27868</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>8164800</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>27307</v>
+        <v>27216</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>8164800</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>27307</v>
+        <v>27216</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>5523840</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>25223</v>
+        <v>25339</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>5523840</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>25223</v>
+        <v>25339</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>8025600</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>26841</v>
+        <v>26752</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>8025600</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>26841</v>
+        <v>26752</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>5429250</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>24791</v>
+        <v>24905</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>5429250</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>24791</v>
+        <v>24905</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>5506690</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>25145</v>
+        <v>25260</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>5506690</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>25145</v>
+        <v>25260</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>5375040</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>24544</v>
+        <v>24656</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>5375040</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>24544</v>
+        <v>24656</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         </is>
       </c>
       <c r="E282" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>5319360</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>24289</v>
+        <v>24401</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>5319360</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>24289</v>
+        <v>24401</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="E314" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>5300080</v>
       </c>
       <c r="I314" s="5" t="n">
-        <v>24201</v>
+        <v>24312</v>
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>5300080</v>
       </c>
       <c r="L314" s="5" t="n">
-        <v>24201</v>
+        <v>24312</v>
       </c>
       <c r="M314" s="3" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="E318" s="4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F318" s="3" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>7645440</v>
       </c>
       <c r="I318" s="5" t="n">
-        <v>25570</v>
+        <v>25485</v>
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>7645440</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>25570</v>
+        <v>25485</v>
       </c>
       <c r="M318" s="3" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         </is>
       </c>
       <c r="E330" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>5208000</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>23781</v>
+        <v>23890</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>5208000</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>23781</v>
+        <v>23890</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         </is>
       </c>
       <c r="E362" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>5080600</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>23199</v>
+        <v>23306</v>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>5080600</v>
       </c>
       <c r="L362" s="5" t="n">
-        <v>23199</v>
+        <v>23306</v>
       </c>
       <c r="M362" s="3" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="E378" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>5043550</v>
       </c>
       <c r="I378" s="5" t="n">
-        <v>23030</v>
+        <v>23136</v>
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>5043550</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>23030</v>
+        <v>23136</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         </is>
       </c>
       <c r="E394" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>5025500</v>
       </c>
       <c r="I394" s="5" t="n">
-        <v>22947</v>
+        <v>23053</v>
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>5025500</v>
       </c>
       <c r="L394" s="5" t="n">
-        <v>22947</v>
+        <v>23053</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="E410" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>5022720</v>
       </c>
       <c r="I410" s="5" t="n">
-        <v>22935</v>
+        <v>23040</v>
       </c>
       <c r="J410" s="3" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>5022720</v>
       </c>
       <c r="L410" s="5" t="n">
-        <v>22935</v>
+        <v>23040</v>
       </c>
       <c r="M410" s="3" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         </is>
       </c>
       <c r="E426" s="4" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>4915300</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>22444</v>
+        <v>22547</v>
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>4915300</v>
       </c>
       <c r="L426" s="5" t="n">
-        <v>22444</v>
+        <v>22547</v>
       </c>
       <c r="M426" s="3" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         </is>
       </c>
       <c r="E446" s="4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F446" s="3" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>7525260</v>
       </c>
       <c r="I446" s="5" t="n">
-        <v>25168</v>
+        <v>25084</v>
       </c>
       <c r="J446" s="3" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>7525260</v>
       </c>
       <c r="L446" s="5" t="n">
-        <v>25168</v>
+        <v>25084</v>
       </c>
       <c r="M446" s="3" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         </is>
       </c>
       <c r="E451" s="4" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>6062900</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>28069</v>
+        <v>27811</v>
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>6062900</v>
       </c>
       <c r="L451" s="5" t="n">
-        <v>28069</v>
+        <v>27811</v>
       </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         </is>
       </c>
       <c r="E461" s="4" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>12320550</v>
       </c>
       <c r="I461" s="5" t="n">
-        <v>29832</v>
+        <v>29904</v>
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>12320550</v>
       </c>
       <c r="L461" s="5" t="n">
-        <v>29832</v>
+        <v>29904</v>
       </c>
       <c r="M461" s="3" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         </is>
       </c>
       <c r="E462" s="4" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
         <v>8678400</v>
       </c>
       <c r="I462" s="5" t="n">
-        <v>33124</v>
+        <v>32998</v>
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>8678400</v>
       </c>
       <c r="L462" s="5" t="n">
-        <v>33124</v>
+        <v>32998</v>
       </c>
       <c r="M462" s="3" t="inlineStr">
         <is>
@@ -29727,9 +29727,9 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>E | 299呎 (1房)
+          <t>E | 300呎 (1房)
 $916万
-$30,630/呎
+$30,528/呎
 (21年-07月-30日)</t>
         </is>
       </c>
@@ -29759,9 +29759,9 @@
       </c>
       <c r="J5" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $626万
-$28,587/呎
+$28,718/呎
 (18年-06月-01日)</t>
         </is>
       </c>
@@ -30029,9 +30029,9 @@
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $623万
-$28,467/呎
+$28,597/呎
 (18年-05月-10日)</t>
         </is>
       </c>
@@ -30132,9 +30132,9 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>E | 299呎 (1房)
+          <t>E | 300呎 (1房)
 $868万
-$29,044/呎
+$28,947/呎
 (18年-08月-28日)</t>
         </is>
       </c>
@@ -30164,9 +30164,9 @@
       </c>
       <c r="J8" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $611万
-$27,906/呎
+$28,034/呎
 (18年-04月-25日)</t>
         </is>
       </c>
@@ -30299,9 +30299,9 @@
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $601万
-$27,437/呎
+$27,563/呎
 (18年-05月-04日)</t>
         </is>
       </c>
@@ -30434,9 +30434,9 @@
       </c>
       <c r="J10" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $569万
-$25,967/呎
+$26,086/呎
 (18年-02月-14日)</t>
         </is>
       </c>
@@ -30569,9 +30569,9 @@
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $593万
-$27,086/呎
+$27,210/呎
 (18年-03月-22日)</t>
         </is>
       </c>
@@ -30704,9 +30704,9 @@
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $567万
-$25,898/呎
+$26,017/呎
 (18年-02月-02日)</t>
         </is>
       </c>
@@ -30807,9 +30807,9 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>E | 299呎 (1房)
+          <t>E | 300呎 (1房)
 $836万
-$27,961/呎
+$27,868/呎
 (18年-07月-11日)</t>
         </is>
       </c>
@@ -30839,9 +30839,9 @@
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $586万
-$26,739/呎
+$26,861/呎
 (18年-03月-20日)</t>
         </is>
       </c>
@@ -31077,9 +31077,9 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>E | 299呎 (1房)
+          <t>E | 300呎 (1房)
 $816万
-$27,307/呎
+$27,216/呎
 (18年-08月-14日)</t>
         </is>
       </c>
@@ -31212,9 +31212,9 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>E | 299呎 (1房)
+          <t>E | 300呎 (1房)
 $803万
-$26,841/呎
+$26,752/呎
 (18年-08月-06日)</t>
         </is>
       </c>
@@ -31244,9 +31244,9 @@
       </c>
       <c r="J16" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $552万
-$25,223/呎
+$25,339/呎
 (18年-01月-31日)</t>
         </is>
       </c>
@@ -31379,9 +31379,9 @@
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $543万
-$24,791/呎
+$24,905/呎
 (18年-01月-03日)</t>
         </is>
       </c>
@@ -31514,9 +31514,9 @@
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $551万
-$25,145/呎
+$25,260/呎
 (18年-01月-10日)</t>
         </is>
       </c>
@@ -31784,9 +31784,9 @@
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $538万
-$24,544/呎
+$24,656/呎
 (17年-12月-11日)</t>
         </is>
       </c>
@@ -32054,9 +32054,9 @@
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $532万
-$24,289/呎
+$24,401/呎
 (17年-12月-28日)</t>
         </is>
       </c>
@@ -32292,9 +32292,9 @@
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>E | 299呎 (1房)
+          <t>E | 300呎 (1房)
 $765万
-$25,570/呎
+$25,485/呎
 (18年-06月-04日)</t>
         </is>
       </c>
@@ -32324,9 +32324,9 @@
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $530万
-$24,201/呎
+$24,312/呎
 (17年-12月-11日)</t>
         </is>
       </c>
@@ -32459,9 +32459,9 @@
       </c>
       <c r="J25" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $521万
-$23,781/呎
+$23,890/呎
 (17年-12月-11日)</t>
         </is>
       </c>
@@ -32729,9 +32729,9 @@
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $508万
-$23,199/呎
+$23,306/呎
 (17年-12月-11日)</t>
         </is>
       </c>
@@ -32864,9 +32864,9 @@
       </c>
       <c r="J28" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $504万
-$23,030/呎
+$23,136/呎
 (17年-12月-11日)</t>
         </is>
       </c>
@@ -32999,9 +32999,9 @@
       </c>
       <c r="J29" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $503万
-$22,947/呎
+$23,053/呎
 (17年-12月-11日)</t>
         </is>
       </c>
@@ -33134,9 +33134,9 @@
       </c>
       <c r="J30" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $502万
-$22,935/呎
+$23,040/呎
 (17年-12月-11日)</t>
         </is>
       </c>
@@ -33269,9 +33269,9 @@
       </c>
       <c r="J31" s="20" t="inlineStr">
         <is>
-          <t>J | 219呎 (开放式)
+          <t>J | 218呎 (开放式)
 $492万
-$22,444/呎
+$22,547/呎
 (17年-12月-07日)</t>
         </is>
       </c>
@@ -33372,9 +33372,9 @@
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>E | 299呎 (1房)
+          <t>E | 300呎 (1房)
 $753万
-$25,168/呎
+$25,084/呎
 (18年-08月-10日)</t>
         </is>
       </c>
@@ -33507,17 +33507,17 @@
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>E | 262呎 (1房)
+          <t>E | 263呎 (1房)
 $868万
-$33,124/呎
+$32,998/呎
 (20年-07月-13日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>F | 413呎 (2房)
+          <t>F | 412呎 (2房)
 $1232万
-$29,832/呎
+$29,904/呎
 (19年-10月-16日)</t>
         </is>
       </c>
@@ -33595,9 +33595,9 @@
       </c>
       <c r="Q33" s="20" t="inlineStr">
         <is>
-          <t>R | 216呎 (开放式)
+          <t>R | 218呎 (开放式)
 $606万
-$28,069/呎
+$27,811/呎
 (19年-05月-22日)</t>
         </is>
       </c>
